--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.56.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.56.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.56.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.56.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: short form of replication. â€œThe Plaintiff replies</t>
+          <t>L92: stray/suspicious non-ASCII glyph(s): U+4ECA CJK UNIFIED IDEOGRAPH-4ECA | isolated marker/symbol line :: 今</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following is the form :â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L21: isolated marker/symbol line :: e.</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -674,11 +678,7 @@
           <t>L65: line starts with digit/letter garbage token | suspicious token(s): 1last (letter/digit mix) | candidate OCR token mismatch vs other OCR: "last" vs "1last" :: 1last answer.</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ na to</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -919,7 +919,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 4</t>
+          <t>L92: stray/suspicious non-ASCII glyph(s): U+4ECA CJK UNIFIED IDEOGRAPH-4ECA | isolated marker/symbol line :: 今</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -966,7 +966,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L96: symbol-only separator/garbage line :: 1850.</t>
+          <t>L93: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1007,7 +1007,11 @@
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="1" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>L96: symbol-only separator/garbage line :: 1850.</t>
+        </is>
+      </c>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
@@ -1033,7 +1037,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1067,7 +1071,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
